--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027D07D7-1F26-4E0F-A2AF-FB365EE47A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5B2F3F-D2FF-4C75-824A-1EEA58DA93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -717,9 +717,6 @@
   </si>
   <si>
     <t>СС по DC</t>
-  </si>
-  <si>
-    <t>Перевести CNY на более старший таймфрейм</t>
   </si>
   <si>
     <t>Использовать kvas или kefir каналы</t>
@@ -1189,6 +1186,33 @@
   </si>
   <si>
     <t>Пофиксить проблемы child_test</t>
+  </si>
+  <si>
+    <t>LWS4_SWATR</t>
+  </si>
+  <si>
+    <t>Изменить оптимизацию на 50% данных оптимизация, 50% тестирование</t>
+  </si>
+  <si>
+    <t>Сетка с учетом позиции. Нужно сделать так, что бы сделки проходили четко по сетке</t>
+  </si>
+  <si>
+    <t>Сетка с трейлер стопом</t>
+  </si>
+  <si>
+    <t>Сетка с выходом по RSI</t>
+  </si>
+  <si>
+    <t>LWS5_ARCHIMEDES</t>
+  </si>
+  <si>
+    <t>LWS5_CADUCEUS</t>
+  </si>
+  <si>
+    <t>Сетка с одним входом и трейлин стопом с автоматическим выбором направления по ADX и SMA</t>
+  </si>
+  <si>
+    <t>LWS6_TIDAL</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1371,6 +1395,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2038,63 +2065,63 @@
         <v>184</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="AL2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AK2" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="AM2" s="2" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="AO2" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="AP2" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="AP2" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="AQ2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AQ2" s="13" t="s">
+      <c r="AR2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AS2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AS2" s="13" t="s">
+      <c r="AT2" s="13" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2136,51 +2163,57 @@
         <v>213</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AI3" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="AO3" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="AP3" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="AP3" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="AQ3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AQ3" s="13" t="s">
+      <c r="AR3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AR3" s="16" t="s">
+      <c r="AS3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AS3" s="14" t="s">
+      <c r="AT3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2219,48 +2252,51 @@
         <v>216</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="AO4" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="AP4" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="AP4" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="AQ4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AQ4" s="13" t="s">
+      <c r="AR4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AR4" s="16" t="s">
+      <c r="AS4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AS4" s="16" t="s">
+      <c r="AT4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2296,42 +2332,45 @@
         <v>218</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="AN5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="AO5" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="AP5" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="AP5" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="AQ5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AQ5" s="13" t="s">
+      <c r="AR5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AR5" s="16" t="s">
+      <c r="AS5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AS5" s="14" t="s">
+      <c r="AT5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2370,45 +2409,45 @@
         <v>220</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>193</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="AL6" s="2" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="AN6" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="AO6" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="AP6" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AP6" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="AQ6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AQ6" s="13" t="s">
+      <c r="AR6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AR6" s="15" t="s">
+      <c r="AS6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AS6" s="13" t="s">
+      <c r="AT6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2447,42 +2486,42 @@
         <v>222</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AO7" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="AP7" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AP7" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="AQ7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AQ7" s="13" t="s">
+      <c r="AR7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AR7" s="13" t="s">
+      <c r="AS7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AS7" s="13" t="s">
+      <c r="AT7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2518,39 +2557,39 @@
         <v>226</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="AL8" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="AM8" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="AN8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="AO8" s="14" t="s">
-        <v>251</v>
+        <v>363</v>
+      </c>
+      <c r="AM8" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="AN8" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="AP8" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AQ8" s="13" t="s">
+      <c r="AR8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AR8" s="14" t="s">
+      <c r="AS8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AS8" s="15" t="s">
+      <c r="AT8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2586,39 +2625,37 @@
         <v>224</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AM9" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="AO9" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="AP9" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="AQ9" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="AN9" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="AP9" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="AQ9" s="21"/>
+      <c r="AR9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AR9" s="13" t="s">
+      <c r="AS9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AS9" s="14" t="s">
+      <c r="AT9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2654,34 +2691,37 @@
         <v>128</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL10" s="2" t="s">
-        <v>380</v>
+        <v>278</v>
+      </c>
+      <c r="AI10" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="AN10" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="AO10" s="15" t="s">
-        <v>255</v>
+        <v>337</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="AP10" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="AQ10" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AQ10" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="AR10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AR10" s="13" t="s">
+      <c r="AS10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AS10" s="13" t="s">
-        <v>237</v>
+      <c r="AT10" s="13" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -2713,36 +2753,42 @@
         <v>193</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="AL11" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="AM11" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="AN11" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AO11" s="15" t="s">
-        <v>254</v>
+        <v>287</v>
+      </c>
+      <c r="AI11" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="AJ11" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AN11" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="AP11" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="AQ11" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="AQ11" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="AR11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AR11" s="13" t="s">
+      <c r="AS11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AS11" s="14" t="s">
+      <c r="AT11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2775,34 +2821,37 @@
         <v>181</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="AM12" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="AN12" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="AO12" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="AP12" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="AQ12" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="AJ12" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="AN12" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="AP12" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="AQ12" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="AR12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AR12" s="14" t="s">
-        <v>253</v>
+      <c r="AS12" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2834,28 +2883,31 @@
         <v>207</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="AO13" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="AP13" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="AQ13" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="AR13" s="13" t="s">
-        <v>304</v>
+        <v>364</v>
+      </c>
+      <c r="AJ13" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="AP13" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="AQ13" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AR13" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="AS13" s="13" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2887,25 +2939,25 @@
         <v>202</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="AO14" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="AP14" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="AQ14" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="AP14" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="AQ14" s="14" t="s">
-        <v>300</v>
+      <c r="AR14" s="14" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2940,22 +2992,22 @@
         <v>225</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI15" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="AO15" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="AP15" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="AQ15" s="14" t="s">
-        <v>302</v>
+      <c r="AP15" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="AQ15" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="AR15" s="14" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2981,16 +3033,16 @@
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AI16" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="AQ16" s="17" t="s">
-        <v>303</v>
+      <c r="AR16" s="17" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
@@ -3016,10 +3068,10 @@
         <v>209</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AI17" s="4" t="s">
         <v>371</v>
@@ -3048,10 +3100,10 @@
         <v>210</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
@@ -3077,7 +3129,7 @@
         <v>211</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
@@ -3103,7 +3155,7 @@
         <v>212</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
@@ -3123,7 +3175,7 @@
         <v>214</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
@@ -3191,7 +3243,7 @@
         <v>179</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
@@ -3205,7 +3257,7 @@
         <v>93</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
@@ -3216,7 +3268,7 @@
         <v>56</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
@@ -3227,7 +3279,7 @@
         <v>57</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
@@ -3238,7 +3290,7 @@
         <v>58</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
@@ -3249,7 +3301,7 @@
         <v>59</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
@@ -3260,7 +3312,7 @@
         <v>60</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
@@ -3420,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -3428,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -3436,7 +3488,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3444,7 +3496,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -3452,7 +3504,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -3460,7 +3512,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -3468,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5B2F3F-D2FF-4C75-824A-1EEA58DA93C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7074B5-0B7A-47C7-BCF9-A5A9A7C77EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="398">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1213,6 +1213,30 @@
   </si>
   <si>
     <t>LWS6_TIDAL</t>
+  </si>
+  <si>
+    <t>Оконный тест с нормализацией для VT</t>
+  </si>
+  <si>
+    <t>Убрать плохие варианты из онлайн теста</t>
+  </si>
+  <si>
+    <t>Добавить новые варианты для Онлайн Теста с учетом оптимизации под новый тест</t>
+  </si>
+  <si>
+    <t>Разобраться с Альфа Инвестициями</t>
+  </si>
+  <si>
+    <t>Разобраться с криптобиржами</t>
+  </si>
+  <si>
+    <t>Стратегия расширяещего усреднения. 1%,2%,4%,8%</t>
+  </si>
+  <si>
+    <t>LWS5_PROGRESSO</t>
+  </si>
+  <si>
+    <t>Плавающий Progresso</t>
   </si>
 </sst>
 </file>
@@ -2097,31 +2121,40 @@
       <c r="AJ2" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="AO2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AP2" s="13" t="s">
+      <c r="AS2" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AT2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AR2" s="13" t="s">
+      <c r="AU2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AV2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AT2" s="13" t="s">
+      <c r="AW2" s="13" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2189,31 +2222,37 @@
       <c r="AJ3" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AM3" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="AO3" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AP3" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AR3" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AP3" s="14" t="s">
+      <c r="AS3" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="AQ3" s="16" t="s">
+      <c r="AT3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AR3" s="13" t="s">
+      <c r="AU3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AS3" s="16" t="s">
+      <c r="AV3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AT3" s="14" t="s">
+      <c r="AW3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2272,31 +2311,34 @@
       <c r="AI4" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="AL4" s="2" t="s">
+      <c r="AM4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AO4" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="AM4" s="2" t="s">
+      <c r="AP4" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="AN4" s="2" t="s">
+      <c r="AQ4" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="AO4" s="2" t="s">
+      <c r="AR4" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AP4" s="13" t="s">
+      <c r="AS4" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AQ4" s="15" t="s">
+      <c r="AT4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AR4" s="13" t="s">
+      <c r="AU4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AS4" s="16" t="s">
+      <c r="AV4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AT4" s="16" t="s">
+      <c r="AW4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2346,31 +2388,34 @@
       <c r="AI5" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="AL5" s="2" t="s">
+      <c r="AM5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="AO5" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AP5" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="AN5" s="2" t="s">
+      <c r="AQ5" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AR5" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AP5" s="14" t="s">
+      <c r="AS5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="AQ5" s="15" t="s">
+      <c r="AT5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AR5" s="13" t="s">
+      <c r="AU5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AS5" s="16" t="s">
+      <c r="AV5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AT5" s="14" t="s">
+      <c r="AW5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2426,28 +2471,28 @@
       <c r="AI6" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AP6" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AN6" s="2" t="s">
+      <c r="AQ6" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="AO6" s="2" t="s">
+      <c r="AR6" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AP6" s="14" t="s">
+      <c r="AS6" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="AQ6" s="15" t="s">
+      <c r="AT6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AR6" s="13" t="s">
+      <c r="AU6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AS6" s="15" t="s">
+      <c r="AV6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AT6" s="13" t="s">
+      <c r="AW6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2500,28 +2545,28 @@
       <c r="AI7" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AP7" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="AN7" s="2" t="s">
+      <c r="AQ7" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AR7" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AP7" s="14" t="s">
+      <c r="AS7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="AQ7" s="15" t="s">
+      <c r="AT7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AR7" s="13" t="s">
+      <c r="AU7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AS7" s="13" t="s">
+      <c r="AV7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AT7" s="13" t="s">
+      <c r="AW7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2568,28 +2613,28 @@
       <c r="AI8" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="AM8" s="20" t="s">
+      <c r="AP8" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="AN8" s="17" t="s">
+      <c r="AQ8" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="AO8" s="2" t="s">
+      <c r="AR8" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AP8" s="14" t="s">
+      <c r="AS8" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AQ8" s="14" t="s">
+      <c r="AT8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AR8" s="13" t="s">
+      <c r="AU8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AS8" s="14" t="s">
+      <c r="AV8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AT8" s="15" t="s">
+      <c r="AW8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2636,26 +2681,26 @@
       <c r="AI9" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="AM9" s="2" t="s">
+      <c r="AP9" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AN9" s="17" t="s">
+      <c r="AQ9" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="AO9" s="2" t="s">
+      <c r="AR9" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AP9" s="13" t="s">
+      <c r="AS9" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="AQ9" s="21"/>
-      <c r="AR9" s="14" t="s">
+      <c r="AT9" s="21"/>
+      <c r="AU9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AS9" s="13" t="s">
+      <c r="AV9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AT9" s="14" t="s">
+      <c r="AW9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2699,28 +2744,28 @@
       <c r="AI10" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="AM10" s="2" t="s">
+      <c r="AP10" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="AN10" s="2" t="s">
+      <c r="AQ10" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AO10" s="2" t="s">
+      <c r="AR10" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AP10" s="15" t="s">
+      <c r="AS10" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="AQ10" s="15" t="s">
+      <c r="AT10" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="AR10" s="14" t="s">
+      <c r="AU10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AS10" s="13" t="s">
+      <c r="AV10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AT10" s="13" t="s">
+      <c r="AW10" s="13" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2767,28 +2812,31 @@
       <c r="AJ11" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="AM11" s="2" t="s">
+      <c r="AL11" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP11" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AN11" s="17" t="s">
+      <c r="AQ11" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="AO11" s="2" t="s">
+      <c r="AR11" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="AP11" s="15" t="s">
+      <c r="AS11" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="AQ11" s="15" t="s">
+      <c r="AT11" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="AR11" s="14" t="s">
+      <c r="AU11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AS11" s="13" t="s">
+      <c r="AV11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AT11" s="14" t="s">
+      <c r="AW11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2835,22 +2883,22 @@
       <c r="AJ12" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="AN12" s="17" t="s">
+      <c r="AQ12" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="AO12" s="2" t="s">
+      <c r="AR12" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="AP12" s="16" t="s">
+      <c r="AS12" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="AQ12" s="14" t="s">
+      <c r="AT12" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AR12" s="15" t="s">
+      <c r="AU12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AS12" s="14" t="s">
+      <c r="AV12" s="14" t="s">
         <v>252</v>
       </c>
     </row>
@@ -2897,16 +2945,16 @@
       <c r="AJ13" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="AP13" s="15" t="s">
+      <c r="AS13" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="AQ13" s="14" t="s">
+      <c r="AT13" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AR13" s="16" t="s">
+      <c r="AU13" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="AS13" s="13" t="s">
+      <c r="AV13" s="13" t="s">
         <v>303</v>
       </c>
     </row>
@@ -2950,13 +2998,13 @@
       <c r="AI14" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="AP14" s="15" t="s">
+      <c r="AS14" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="AQ14" s="16" t="s">
+      <c r="AT14" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="AR14" s="14" t="s">
+      <c r="AU14" s="14" t="s">
         <v>299</v>
       </c>
     </row>
@@ -3000,13 +3048,13 @@
       <c r="AI15" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="AP15" s="13" t="s">
+      <c r="AS15" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="AQ15" s="15" t="s">
+      <c r="AT15" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="AR15" s="14" t="s">
+      <c r="AU15" s="14" t="s">
         <v>301</v>
       </c>
     </row>
@@ -3041,7 +3089,7 @@
       <c r="AI16" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="AR16" s="17" t="s">
+      <c r="AU16" s="17" t="s">
         <v>302</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7074B5-0B7A-47C7-BCF9-A5A9A7C77EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5538A2-B24A-4762-ACF8-A33C87B0628D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="402">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1237,6 +1237,18 @@
   </si>
   <si>
     <t>Плавающий Progresso</t>
+  </si>
+  <si>
+    <t>LWS7_FLOATGRESSO</t>
+  </si>
+  <si>
+    <t>Добавить в тест данные о размере позиции</t>
+  </si>
+  <si>
+    <t>Добавить в тест данные о текущей нереализованной прибыли</t>
+  </si>
+  <si>
+    <t>LWS5_XPG</t>
   </si>
 </sst>
 </file>
@@ -1705,17 +1717,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="24" width="28.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="28.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="27.42578125" style="2" customWidth="1"/>
-    <col min="27" max="110" width="27.28515625" style="2" customWidth="1"/>
-    <col min="111" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="24" width="28.26953125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.453125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="27.453125" style="2" customWidth="1"/>
+    <col min="27" max="110" width="27.26953125" style="2" customWidth="1"/>
+    <col min="111" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3">
         <v>45747</v>
@@ -2045,7 +2057,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2158,7 +2170,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2222,11 +2234,14 @@
       <c r="AJ3" s="4" t="s">
         <v>385</v>
       </c>
+      <c r="AL3" s="4" t="s">
+        <v>397</v>
+      </c>
       <c r="AM3" s="2" t="s">
         <v>390</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AO3" s="2" t="s">
         <v>382</v>
@@ -2256,7 +2271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:110" ht="87" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2314,6 +2329,9 @@
       <c r="AM4" s="2" t="s">
         <v>391</v>
       </c>
+      <c r="AN4" s="2" t="s">
+        <v>400</v>
+      </c>
       <c r="AO4" s="2" t="s">
         <v>384</v>
       </c>
@@ -2342,7 +2360,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2419,7 +2437,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2496,7 +2514,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2570,7 +2588,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2638,7 +2656,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2704,7 +2722,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2769,7 +2787,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2840,7 +2858,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:110" ht="165" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:110" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2883,6 +2901,9 @@
       <c r="AJ12" s="4" t="s">
         <v>387</v>
       </c>
+      <c r="AL12" s="4" t="s">
+        <v>398</v>
+      </c>
       <c r="AQ12" s="17" t="s">
         <v>350</v>
       </c>
@@ -2902,7 +2923,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2945,6 +2966,9 @@
       <c r="AJ13" s="4" t="s">
         <v>389</v>
       </c>
+      <c r="AL13" s="4" t="s">
+        <v>401</v>
+      </c>
       <c r="AS13" s="15" t="s">
         <v>257</v>
       </c>
@@ -2958,7 +2982,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3008,7 +3032,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3058,7 +3082,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3093,7 +3117,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3125,7 +3149,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3154,7 +3178,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3180,7 +3204,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3206,7 +3230,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3226,7 +3250,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3243,7 +3267,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3260,7 +3284,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3277,7 +3301,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3294,7 +3318,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3308,7 +3332,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3319,7 +3343,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3330,7 +3354,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3341,7 +3365,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3352,7 +3376,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3363,7 +3387,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3371,7 +3395,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -3379,92 +3403,92 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3478,19 +3502,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FB18B6-8CBA-4D69-B652-AA868883124A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="10"/>
-    <col min="2" max="2" width="54.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="10"/>
+    <col min="2" max="2" width="54.81640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="45.1796875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -3509,13 +3533,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BCABFF-B4AE-4771-9DE2-5CE17DADACE8}">
   <dimension ref="A2:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" style="18" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="36.7265625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3523,7 +3547,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3531,7 +3555,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3539,7 +3563,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3547,7 +3571,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3555,7 +3579,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3563,7 +3587,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3571,97 +3595,97 @@
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5538A2-B24A-4762-ACF8-A33C87B0628D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023A3633-5DD1-4FF4-9BC4-D00C52719893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="404">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1249,6 +1249,12 @@
   </si>
   <si>
     <t>LWS5_XPG</t>
+  </si>
+  <si>
+    <t>Сетка по уровням зигзага с определением тренда</t>
+  </si>
+  <si>
+    <t>Сетка по фракталам. Очень легко определять направление, нужно смотреть перекрываются ли фракталы</t>
   </si>
 </sst>
 </file>
@@ -1717,17 +1723,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF51"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="24" width="28.26953125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="28.453125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="27.453125" style="2" customWidth="1"/>
-    <col min="27" max="110" width="27.26953125" style="2" customWidth="1"/>
-    <col min="111" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="24" width="28.28515625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="27.42578125" style="2" customWidth="1"/>
+    <col min="27" max="110" width="27.28515625" style="2" customWidth="1"/>
+    <col min="111" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3">
         <v>45747</v>
@@ -2057,7 +2063,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:110" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2136,41 +2142,41 @@
       <c r="AL2" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="AM2" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AP2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AS2" s="13" t="s">
+      <c r="AU2" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AT2" s="14" t="s">
+      <c r="AV2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AW2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AV2" s="15" t="s">
+      <c r="AX2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AW2" s="13" t="s">
+      <c r="AY2" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2237,41 +2243,41 @@
       <c r="AL3" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="AM3" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="AO3" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AR3" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AS3" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AT3" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AS3" s="14" t="s">
+      <c r="AU3" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="AT3" s="16" t="s">
+      <c r="AV3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AU3" s="13" t="s">
+      <c r="AW3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AV3" s="16" t="s">
+      <c r="AX3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AW3" s="14" t="s">
+      <c r="AY3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:110" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2326,41 +2332,41 @@
       <c r="AI4" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="AM4" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="AN4" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="AO4" s="2" t="s">
+      <c r="AL4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="AP4" s="2" t="s">
+      <c r="AR4" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="AQ4" s="2" t="s">
+      <c r="AS4" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="AR4" s="2" t="s">
+      <c r="AT4" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AS4" s="13" t="s">
+      <c r="AU4" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AT4" s="15" t="s">
+      <c r="AV4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AU4" s="13" t="s">
+      <c r="AW4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AV4" s="16" t="s">
+      <c r="AX4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AW4" s="16" t="s">
+      <c r="AY4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2406,38 +2412,41 @@
       <c r="AI5" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="AM5" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="AO5" s="2" t="s">
+      <c r="AL5" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="AP5" s="2" t="s">
+      <c r="AR5" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="AQ5" s="2" t="s">
+      <c r="AS5" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="AR5" s="2" t="s">
+      <c r="AT5" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AS5" s="14" t="s">
+      <c r="AU5" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="AT5" s="15" t="s">
+      <c r="AV5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AU5" s="13" t="s">
+      <c r="AW5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AV5" s="16" t="s">
+      <c r="AX5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AW5" s="14" t="s">
+      <c r="AY5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:110" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2490,31 +2499,34 @@
         <v>376</v>
       </c>
       <c r="AP6" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="AR6" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AQ6" s="2" t="s">
+      <c r="AS6" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="AR6" s="2" t="s">
+      <c r="AT6" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AS6" s="14" t="s">
+      <c r="AU6" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="AT6" s="15" t="s">
+      <c r="AV6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AU6" s="13" t="s">
+      <c r="AW6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AV6" s="15" t="s">
+      <c r="AX6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AW6" s="13" t="s">
+      <c r="AY6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2563,32 +2575,32 @@
       <c r="AI7" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="AP7" s="2" t="s">
+      <c r="AR7" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="AQ7" s="2" t="s">
+      <c r="AS7" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AT7" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AS7" s="14" t="s">
+      <c r="AU7" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="AT7" s="15" t="s">
+      <c r="AV7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AU7" s="13" t="s">
+      <c r="AW7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AV7" s="13" t="s">
+      <c r="AX7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AW7" s="13" t="s">
+      <c r="AY7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2631,32 +2643,32 @@
       <c r="AI8" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="AP8" s="20" t="s">
+      <c r="AR8" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="AQ8" s="17" t="s">
+      <c r="AS8" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AT8" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AS8" s="14" t="s">
+      <c r="AU8" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AT8" s="14" t="s">
+      <c r="AV8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AU8" s="13" t="s">
+      <c r="AW8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AV8" s="14" t="s">
+      <c r="AX8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AW8" s="15" t="s">
+      <c r="AY8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2699,30 +2711,30 @@
       <c r="AI9" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="AP9" s="2" t="s">
+      <c r="AR9" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AQ9" s="17" t="s">
+      <c r="AS9" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="AR9" s="2" t="s">
+      <c r="AT9" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AS9" s="13" t="s">
+      <c r="AU9" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="AT9" s="21"/>
-      <c r="AU9" s="14" t="s">
+      <c r="AV9" s="21"/>
+      <c r="AW9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AV9" s="13" t="s">
+      <c r="AX9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AW9" s="14" t="s">
+      <c r="AY9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2762,32 +2774,32 @@
       <c r="AI10" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="AP10" s="2" t="s">
+      <c r="AR10" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="AQ10" s="2" t="s">
+      <c r="AS10" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AR10" s="2" t="s">
+      <c r="AT10" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AS10" s="15" t="s">
+      <c r="AU10" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="AT10" s="15" t="s">
+      <c r="AV10" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="AU10" s="14" t="s">
+      <c r="AW10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AV10" s="13" t="s">
+      <c r="AX10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AW10" s="13" t="s">
+      <c r="AY10" s="13" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="11" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2833,32 +2845,32 @@
       <c r="AL11" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="AP11" s="2" t="s">
+      <c r="AR11" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AQ11" s="17" t="s">
+      <c r="AS11" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="AR11" s="2" t="s">
+      <c r="AT11" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="AS11" s="15" t="s">
+      <c r="AU11" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="AT11" s="15" t="s">
+      <c r="AV11" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="AU11" s="14" t="s">
+      <c r="AW11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AV11" s="13" t="s">
+      <c r="AX11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AW11" s="14" t="s">
+      <c r="AY11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:110" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:110" ht="165" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2904,26 +2916,26 @@
       <c r="AL12" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="AQ12" s="17" t="s">
+      <c r="AS12" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="AR12" s="2" t="s">
+      <c r="AT12" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="AS12" s="16" t="s">
+      <c r="AU12" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="AT12" s="14" t="s">
+      <c r="AV12" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AU12" s="15" t="s">
+      <c r="AW12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AV12" s="14" t="s">
+      <c r="AX12" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2969,20 +2981,20 @@
       <c r="AL13" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="AS13" s="15" t="s">
+      <c r="AU13" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="AT13" s="14" t="s">
+      <c r="AV13" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AU13" s="16" t="s">
+      <c r="AW13" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="AV13" s="13" t="s">
+      <c r="AX13" s="13" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="14" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3022,17 +3034,17 @@
       <c r="AI14" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="AS14" s="15" t="s">
+      <c r="AU14" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="AT14" s="16" t="s">
+      <c r="AV14" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="AU14" s="14" t="s">
+      <c r="AW14" s="14" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3072,17 +3084,17 @@
       <c r="AI15" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="AS15" s="13" t="s">
+      <c r="AU15" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="AT15" s="15" t="s">
+      <c r="AV15" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="AU15" s="14" t="s">
+      <c r="AW15" s="14" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="16" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3113,11 +3125,11 @@
       <c r="AI16" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="AU16" s="17" t="s">
+      <c r="AW16" s="17" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3149,7 +3161,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3178,7 +3190,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3204,7 +3216,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3230,7 +3242,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3250,7 +3262,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3267,7 +3279,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3284,7 +3296,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3301,7 +3313,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3318,7 +3330,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3332,7 +3344,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3343,7 +3355,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3354,7 +3366,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3365,7 +3377,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3376,7 +3388,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3387,7 +3399,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3395,7 +3407,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -3403,92 +3415,92 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3502,19 +3514,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FB18B6-8CBA-4D69-B652-AA868883124A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="10"/>
-    <col min="2" max="2" width="54.81640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="45.1796875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="10"/>
+    <col min="2" max="2" width="54.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -3533,13 +3545,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BCABFF-B4AE-4771-9DE2-5CE17DADACE8}">
   <dimension ref="A2:B27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" customWidth="1"/>
-    <col min="2" max="2" width="36.7265625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3547,7 +3559,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3555,7 +3567,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3563,7 +3575,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3571,7 +3583,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3579,7 +3591,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3587,7 +3599,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3595,97 +3607,97 @@
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023A3633-5DD1-4FF4-9BC4-D00C52719893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762D6B95-7449-467D-91C8-B916FE35BADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="406">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1255,6 +1255,12 @@
   </si>
   <si>
     <t>Сетка по фракталам. Очень легко определять направление, нужно смотреть перекрываются ли фракталы</t>
+  </si>
+  <si>
+    <t>Настроить роботов на торговлю под инструменты с учетом нового теста</t>
+  </si>
+  <si>
+    <t>Переделать window_test в класс. Добавить такие же возможности, как в RL2.</t>
   </si>
 </sst>
 </file>
@@ -2142,6 +2148,9 @@
       <c r="AL2" s="4" t="s">
         <v>395</v>
       </c>
+      <c r="AM2" s="4" t="s">
+        <v>390</v>
+      </c>
       <c r="AO2" s="2" t="s">
         <v>402</v>
       </c>
@@ -2335,8 +2344,11 @@
       <c r="AL4" s="4" t="s">
         <v>393</v>
       </c>
+      <c r="AO4" s="20" t="s">
+        <v>404</v>
+      </c>
       <c r="AP4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ4" s="2" t="s">
         <v>384</v>
@@ -2415,8 +2427,11 @@
       <c r="AL5" s="4" t="s">
         <v>399</v>
       </c>
+      <c r="AO5" s="2" t="s">
+        <v>405</v>
+      </c>
       <c r="AP5" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ5" s="2" t="s">
         <v>388</v>
@@ -2498,8 +2513,8 @@
       <c r="AI6" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="AP6" s="2" t="s">
-        <v>392</v>
+      <c r="AL6" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="AR6" s="2" t="s">
         <v>352</v>
@@ -2575,6 +2590,9 @@
       <c r="AI7" s="4" t="s">
         <v>362</v>
       </c>
+      <c r="AL7" s="4" t="s">
+        <v>398</v>
+      </c>
       <c r="AR7" s="2" t="s">
         <v>353</v>
       </c>
@@ -2643,6 +2661,9 @@
       <c r="AI8" s="4" t="s">
         <v>363</v>
       </c>
+      <c r="AL8" s="4" t="s">
+        <v>401</v>
+      </c>
       <c r="AR8" s="20" t="s">
         <v>377</v>
       </c>
@@ -2842,9 +2863,6 @@
       <c r="AJ11" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="AL11" s="4" t="s">
-        <v>396</v>
-      </c>
       <c r="AR11" s="2" t="s">
         <v>380</v>
       </c>
@@ -2913,9 +2931,6 @@
       <c r="AJ12" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="AL12" s="4" t="s">
-        <v>398</v>
-      </c>
       <c r="AS12" s="17" t="s">
         <v>350</v>
       </c>
@@ -2977,9 +2992,6 @@
       </c>
       <c r="AJ13" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="AL13" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="AU13" s="15" t="s">
         <v>257</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762D6B95-7449-467D-91C8-B916FE35BADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81182449-065F-4CEE-998D-85C68C8F6FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="408">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1261,6 +1261,12 @@
   </si>
   <si>
     <t>Переделать window_test в класс. Добавить такие же возможности, как в RL2.</t>
+  </si>
+  <si>
+    <t>LWS5_EUCLID</t>
+  </si>
+  <si>
+    <t>LWS5_MERCATUS</t>
   </si>
 </sst>
 </file>
@@ -2252,11 +2258,14 @@
       <c r="AL3" s="4" t="s">
         <v>397</v>
       </c>
+      <c r="AM3" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="AO3" s="2" t="s">
         <v>403</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="AQ3" s="2" t="s">
         <v>382</v>
@@ -2344,11 +2353,11 @@
       <c r="AL4" s="4" t="s">
         <v>393</v>
       </c>
+      <c r="AM4" s="4" t="s">
+        <v>400</v>
+      </c>
       <c r="AO4" s="20" t="s">
         <v>404</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="AQ4" s="2" t="s">
         <v>384</v>
@@ -2430,9 +2439,6 @@
       <c r="AO5" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AP5" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="AQ5" s="2" t="s">
         <v>388</v>
       </c>
@@ -2593,6 +2599,9 @@
       <c r="AL7" s="4" t="s">
         <v>398</v>
       </c>
+      <c r="AM7" s="4" t="s">
+        <v>406</v>
+      </c>
       <c r="AR7" s="2" t="s">
         <v>353</v>
       </c>
@@ -2663,6 +2672,9 @@
       </c>
       <c r="AL8" s="4" t="s">
         <v>401</v>
+      </c>
+      <c r="AM8" s="4" t="s">
+        <v>407</v>
       </c>
       <c r="AR8" s="20" t="s">
         <v>377</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81182449-065F-4CEE-998D-85C68C8F6FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C64BEE7-607D-40CB-9C2E-FBA641E05033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="411">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1267,6 +1267,15 @@
   </si>
   <si>
     <t>LWS5_MERCATUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реверс-гэповая стратегия. Выставляет вечером реверс пару. С утра закрываем прибыльную сделку с гэпа, убыточную оставляем до закрытия гэпа. </t>
+  </si>
+  <si>
+    <t>Добавить opener (RL2) для сделок руками</t>
+  </si>
+  <si>
+    <t>Риск-менеджмент на интрусемент для RL1 и RL2</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1306,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1376,6 +1385,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1389,7 +1404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1452,6 +1467,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2157,6 +2175,9 @@
       <c r="AM2" s="4" t="s">
         <v>390</v>
       </c>
+      <c r="AN2" s="2" t="s">
+        <v>409</v>
+      </c>
       <c r="AO2" s="2" t="s">
         <v>402</v>
       </c>
@@ -2359,6 +2380,9 @@
       <c r="AO4" s="20" t="s">
         <v>404</v>
       </c>
+      <c r="AP4" s="2" t="s">
+        <v>408</v>
+      </c>
       <c r="AQ4" s="2" t="s">
         <v>384</v>
       </c>
@@ -2521,6 +2545,9 @@
       </c>
       <c r="AL6" s="4" t="s">
         <v>396</v>
+      </c>
+      <c r="AO6" s="22" t="s">
+        <v>410</v>
       </c>
       <c r="AR6" s="2" t="s">
         <v>352</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C64BEE7-607D-40CB-9C2E-FBA641E05033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2F7AD-940F-4E95-BF28-BD03BEB0708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="410">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Запустить торговлю на акциях моех</t>
   </si>
   <si>
-    <t>Добавить риск-менеджмент в QT</t>
-  </si>
-  <si>
     <t>Добавить тайм-менеджмент в QT</t>
   </si>
   <si>
@@ -1053,9 +1050,6 @@
   </si>
   <si>
     <t>Сосредоточиться на своем счете мосбиржи</t>
-  </si>
-  <si>
-    <t>Тест через оконные функции (rolling)</t>
   </si>
   <si>
     <t>QuikTraider3</t>
@@ -1089,29 +1083,10 @@
     <t>LWS1_AUTOGRID</t>
   </si>
   <si>
-    <t>Парный противоположный грид. Один инструмент в шорт, другой в лонг. Сетки и размеры одинаковы. Если на одном инструменте 3 лонга, то на другом 3 шорта. Прибыль засчет хода внутри сетки. Если случается выход за сетку, то один инструмент будет компенсировать другой.</t>
-  </si>
-  <si>
-    <t>Парный Грид с переходом в хедж</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSI-грид-хедж
-Инструмент A: [2, 2, 1, 0, 0, -1, -2, -2] 
-Инструмент B: [-2, -1, 0, 0, 1, 2, 2, 2] </t>
-  </si>
-  <si>
-    <t>(3,2,1,0,0,-1,-2,-3). А другого (0,-1,-2,-3,3,2,1)</t>
-  </si>
-  <si>
     <t>Плавающий грид по DC</t>
   </si>
   <si>
     <t>Процентная сетка от скользящей средней</t>
-  </si>
-  <si>
-    <t>обнуляющий парный грид.
-Лонг:  [0, 3, 2, 1, 0 ]
-Шорт: [0, -1, -2, -3, 0]</t>
   </si>
   <si>
     <t>Пробойная парная стратегия по BB от центра. В центра открытие лонга и шорта. При выходе к верху закрытие шорта и удержание лонга и наоборот</t>
@@ -1182,9 +1157,6 @@
     <t>ST_mini (RL2)</t>
   </si>
   <si>
-    <t>плавающий грид с четким выходом на 1 лвле</t>
-  </si>
-  <si>
     <t>Пофиксить проблемы child_test</t>
   </si>
   <si>
@@ -1275,7 +1247,29 @@
     <t>Добавить opener (RL2) для сделок руками</t>
   </si>
   <si>
-    <t>Риск-менеджмент на интрусемент для RL1 и RL2</t>
+    <t>Старатегия BB + быстрая MA. Полосы от широкого BB добавляются к быстрой МА.
+И у нас автоматически определяются точки входа в лонг и шорт. По сути данный робот будет автоматически определеять режим рынка</t>
+  </si>
+  <si>
+    <t>Риск-менеджмент на инструмент для RL1 и RL2</t>
+  </si>
+  <si>
+    <t>Добавить риск-менеджмент в QT (RL1)</t>
+  </si>
+  <si>
+    <t>динамическая сетка по волатильности и adx</t>
+  </si>
+  <si>
+    <t>ADX_DEHAKA. При тренде дехака, без тренда johanna</t>
+  </si>
+  <si>
+    <t>Канал n_atr</t>
+  </si>
+  <si>
+    <t>Убрать большие периоды из оптимизаций</t>
+  </si>
+  <si>
+    <t>Собрать набор полуавтоматических спекулятивных стратегий. Типа STA_mini.</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1300,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1391,6 +1385,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1404,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1470,6 +1494,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2093,7 +2132,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2107,112 +2146,109 @@
         <v>39</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG2" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="AH2" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="AH2" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="AI2" s="4" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="AP2" s="2" t="s">
         <v>394</v>
       </c>
+      <c r="AP2" s="22" t="s">
+        <v>384</v>
+      </c>
       <c r="AQ2" s="2" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>315</v>
+        <v>350</v>
+      </c>
+      <c r="AS2" s="22" t="s">
+        <v>314</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AU2" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AV2" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AW2" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AX2" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AY2" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:110" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2226,94 +2262,91 @@
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AI3" s="19" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>316</v>
+        <v>395</v>
+      </c>
+      <c r="AQ3" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="AR3" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="AS3" s="22" t="s">
+        <v>315</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AV3" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AX3" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AY3" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
@@ -2330,88 +2363,88 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="O4" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="AL4" s="4" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="AM4" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="AO4" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="AP4" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="AO4" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="AQ4" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>367</v>
+        <v>376</v>
+      </c>
+      <c r="AR4" s="21" t="s">
+        <v>370</v>
       </c>
       <c r="AS4" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AT4" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AU4" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AV4" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AW4" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AX4" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AY4" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:110" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2425,73 +2458,79 @@
         <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG5" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="AH5" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="AH5" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="AI5" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="AL5" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
+      </c>
+      <c r="AP5" s="23" t="s">
+        <v>402</v>
       </c>
       <c r="AQ5" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>351</v>
+        <v>380</v>
+      </c>
+      <c r="AR5" s="24" t="s">
+        <v>371</v>
       </c>
       <c r="AS5" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AT5" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AU5" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AV5" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AW5" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AX5" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AY5" s="14" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2505,73 +2544,79 @@
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="AO6" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AS6" s="2" t="s">
-        <v>319</v>
+        <v>388</v>
+      </c>
+      <c r="AM6" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="AO6" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="AP6" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="AR6" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS6" s="21" t="s">
+        <v>349</v>
       </c>
       <c r="AT6" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AU6" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AV6" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AW6" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AX6" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AY6" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2588,70 +2633,73 @@
         <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG7" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI7" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="AL7" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="AM7" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="AO7" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="AS7" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="AH7" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="AI7" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="AL7" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="AM7" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="AS7" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="AT7" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AU7" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AV7" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AW7" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AX7" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AY7" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
@@ -2668,64 +2716,64 @@
         <v>38</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="AR8" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="AS8" s="17" t="s">
-        <v>355</v>
+        <v>403</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AU8" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AV8" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AW8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="AX8" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="AY8" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -2739,59 +2787,56 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="AS9" s="17" t="s">
-        <v>324</v>
+        <v>344</v>
+      </c>
+      <c r="AS9" s="21" t="s">
+        <v>405</v>
       </c>
       <c r="AT9" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AU9" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AV9" s="21"/>
       <c r="AW9" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="AX9" s="13" t="s">
-        <v>41</v>
+        <v>220</v>
       </c>
       <c r="AY9" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2805,58 +2850,61 @@
         <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>374</v>
+        <v>367</v>
+      </c>
+      <c r="AM10" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="AS10" s="2" t="s">
-        <v>337</v>
+        <v>406</v>
+      </c>
+      <c r="AS10" s="21" t="s">
+        <v>407</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AU10" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AV10" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AW10" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="AX10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AX10" s="13" t="s">
-        <v>117</v>
-      </c>
       <c r="AY10" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -2870,64 +2918,58 @@
         <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="AR11" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="AS11" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="AT11" s="2" t="s">
-        <v>327</v>
+        <v>378</v>
+      </c>
+      <c r="AM11" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="AU11" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AV11" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AX11" s="13" t="s">
         <v>35</v>
       </c>
       <c r="AY11" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:110" ht="165" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2938,55 +2980,49 @@
         <v>25</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AJ12" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="AS12" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="AT12" s="2" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="AU12" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AV12" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AW12" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AX12" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -3000,49 +3036,49 @@
         <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="AU13" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="AV13" s="14" t="s">
-        <v>264</v>
+        <v>381</v>
+      </c>
+      <c r="AU13" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="AV13" s="25" t="s">
+        <v>263</v>
       </c>
       <c r="AW13" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AX13" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -3056,43 +3092,43 @@
         <v>27</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="AU14" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="AV14" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="AV14" s="16" t="s">
-        <v>268</v>
-      </c>
       <c r="AW14" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -3106,43 +3142,43 @@
         <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AU15" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AV15" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -3153,31 +3189,31 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI16" s="4" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="AW16" s="17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
@@ -3188,28 +3224,28 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.25">
@@ -3223,22 +3259,22 @@
         <v>37</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
@@ -3249,22 +3285,22 @@
         <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
@@ -3275,22 +3311,22 @@
         <v>19</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
@@ -3298,19 +3334,19 @@
         <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
@@ -3318,16 +3354,16 @@
         <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
@@ -3335,16 +3371,16 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
@@ -3352,16 +3388,16 @@
         <v>23</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
@@ -3369,16 +3405,16 @@
         <v>24</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
@@ -3386,13 +3422,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
@@ -3400,10 +3436,10 @@
         <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
@@ -3411,10 +3447,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
@@ -3422,10 +3458,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.25">
@@ -3433,10 +3469,10 @@
         <v>29</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.25">
@@ -3444,10 +3480,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.25">
@@ -3455,7 +3491,7 @@
         <v>31</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3463,7 +3499,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3574,7 +3610,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -3582,10 +3618,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3607,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -3615,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -3623,7 +3659,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3631,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -3639,7 +3675,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -3647,7 +3683,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -3655,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2F7AD-940F-4E95-BF28-BD03BEB0708E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F833C4-5544-4EDF-89CF-A523BF5242FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="415">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1270,6 +1270,21 @@
   </si>
   <si>
     <t>Собрать набор полуавтоматических спекулятивных стратегий. Типа STA_mini.</t>
+  </si>
+  <si>
+    <t>CheckWSTrader</t>
+  </si>
+  <si>
+    <t>Roll max процентного отношения цены к BBU и к BBD. Таким образом можно определить точки входа</t>
+  </si>
+  <si>
+    <t>Направленный алкаш для RL2 может быть весьма интересным решением</t>
+  </si>
+  <si>
+    <t>Фикс проблем и добавление новый фичей в CheckWSTrader</t>
+  </si>
+  <si>
+    <t>Обновление child_test</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1315,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1387,12 +1402,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1400,12 +1409,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1428,7 +1431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1503,12 +1506,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2214,37 +2211,40 @@
       <c r="AM2" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AN2" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AP2" s="22" t="s">
+      <c r="AR2" s="22" t="s">
         <v>384</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="AS2" s="22" t="s">
+      <c r="AU2" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="AU2" s="13" t="s">
+      <c r="AW2" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="AV2" s="14" t="s">
+      <c r="AX2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="AW2" s="13" t="s">
+      <c r="AY2" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AX2" s="15" t="s">
+      <c r="AZ2" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="AY2" s="13" t="s">
+      <c r="BA2" s="13" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2318,34 +2318,40 @@
       <c r="AM3" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AN3" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AQ3" s="22" t="s">
+      <c r="AR3" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="AS3" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="AR3" s="22" t="s">
+      <c r="AT3" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="AS3" s="22" t="s">
+      <c r="AU3" s="22" t="s">
         <v>315</v>
       </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AV3" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AU3" s="14" t="s">
+      <c r="AW3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="AV3" s="16" t="s">
+      <c r="AX3" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="AW3" s="13" t="s">
+      <c r="AY3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AX3" s="16" t="s">
+      <c r="AZ3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="AY3" s="14" t="s">
+      <c r="BA3" s="14" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2410,37 +2416,40 @@
       <c r="AM4" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="AO4" s="20" t="s">
+      <c r="AN4" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="AQ4" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="AP4" s="2" t="s">
+      <c r="AR4" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="AQ4" s="2" t="s">
+      <c r="AS4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AR4" s="21" t="s">
+      <c r="AT4" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="AS4" s="2" t="s">
+      <c r="AU4" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AT4" s="2" t="s">
+      <c r="AV4" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AU4" s="13" t="s">
+      <c r="AW4" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AV4" s="15" t="s">
+      <c r="AX4" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AW4" s="13" t="s">
+      <c r="AY4" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AX4" s="16" t="s">
+      <c r="AZ4" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="AY4" s="16" t="s">
+      <c r="BA4" s="16" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2496,37 +2505,37 @@
       <c r="AM5" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="AO5" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="AP5" s="23" t="s">
+      <c r="AQ5" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="AR5" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="AQ5" s="2" t="s">
+      <c r="AS5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AR5" s="24" t="s">
+      <c r="AT5" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="AS5" s="2" t="s">
+      <c r="AU5" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AT5" s="2" t="s">
+      <c r="AV5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AU5" s="14" t="s">
+      <c r="AW5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="AV5" s="15" t="s">
+      <c r="AX5" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="AW5" s="13" t="s">
+      <c r="AY5" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AX5" s="16" t="s">
+      <c r="AZ5" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="AY5" s="14" t="s">
+      <c r="BA5" s="14" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2588,34 +2597,31 @@
       <c r="AM6" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="AO6" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="AP6" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="AR6" s="22" t="s">
+      <c r="AQ6" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT6" s="22" t="s">
         <v>359</v>
       </c>
-      <c r="AS6" s="21" t="s">
+      <c r="AU6" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="AT6" s="2" t="s">
+      <c r="AV6" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AU6" s="14" t="s">
+      <c r="AW6" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="AV6" s="15" t="s">
+      <c r="AX6" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AW6" s="13" t="s">
+      <c r="AY6" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AX6" s="15" t="s">
+      <c r="AZ6" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="AY6" s="13" t="s">
+      <c r="BA6" s="13" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2674,31 +2680,31 @@
       <c r="AM7" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="AO7" s="27" t="s">
-        <v>409</v>
-      </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AQ7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="AT7" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AS7" s="21" t="s">
+      <c r="AU7" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AV7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AU7" s="14" t="s">
+      <c r="AW7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="AV7" s="15" t="s">
+      <c r="AX7" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AW7" s="13" t="s">
+      <c r="AY7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AX7" s="13" t="s">
+      <c r="AZ7" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="AY7" s="13" t="s">
+      <c r="BA7" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2751,28 +2757,28 @@
       <c r="AM8" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AT8" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AS8" s="2" t="s">
+      <c r="AU8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AT8" s="2" t="s">
+      <c r="AV8" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AU8" s="14" t="s">
+      <c r="AW8" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="AV8" s="14" t="s">
+      <c r="AX8" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="AW8" s="13" t="s">
+      <c r="AY8" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AX8" s="14" t="s">
+      <c r="AZ8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="AY8" s="15" t="s">
+      <c r="BA8" s="15" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2819,23 +2825,26 @@
       <c r="AI9" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="AR9" s="2" t="s">
+      <c r="AM9" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="AT9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="AS9" s="21" t="s">
+      <c r="AU9" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="AT9" s="2" t="s">
+      <c r="AV9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AU9" s="13" t="s">
+      <c r="AW9" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="AV9" s="21"/>
-      <c r="AW9" s="14" t="s">
+      <c r="AX9" s="21"/>
+      <c r="AY9" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="AY9" s="14" t="s">
+      <c r="BA9" s="14" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2880,30 +2889,30 @@
         <v>367</v>
       </c>
       <c r="AM10" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="AR10" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="AT10" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="AS10" s="21" t="s">
+      <c r="AU10" s="21" t="s">
         <v>407</v>
       </c>
-      <c r="AT10" s="2" t="s">
+      <c r="AV10" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AU10" s="15" t="s">
+      <c r="AW10" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="AV10" s="15" t="s">
+      <c r="AX10" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="AW10" s="14" t="s">
+      <c r="AY10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="AX10" s="13" t="s">
+      <c r="AZ10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AY10" s="13" t="s">
+      <c r="BA10" s="13" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2951,21 +2960,21 @@
         <v>378</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="AU11" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="AW11" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="AV11" s="15" t="s">
+      <c r="AX11" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="AW11" s="14" t="s">
+      <c r="AY11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="AX11" s="13" t="s">
+      <c r="AZ11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AY11" s="14" t="s">
+      <c r="BA11" s="14" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3012,16 +3021,19 @@
       <c r="AJ12" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="AU12" s="16" t="s">
+      <c r="AM12" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW12" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="AV12" s="14" t="s">
+      <c r="AX12" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AW12" s="15" t="s">
+      <c r="AY12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AX12" s="14" t="s">
+      <c r="AZ12" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3068,16 +3080,16 @@
       <c r="AJ13" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="AU13" s="25" t="s">
+      <c r="AW13" s="24" t="s">
         <v>256</v>
       </c>
-      <c r="AV13" s="25" t="s">
+      <c r="AX13" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="AW13" s="16" t="s">
+      <c r="AY13" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="AX13" s="13" t="s">
+      <c r="AZ13" s="13" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3121,13 +3133,13 @@
       <c r="AI14" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="AU14" s="15" t="s">
+      <c r="AW14" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="AV14" s="25" t="s">
+      <c r="AX14" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="AW14" s="14" t="s">
+      <c r="AY14" s="14" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3171,13 +3183,13 @@
       <c r="AI15" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="AU15" s="13" t="s">
+      <c r="AW15" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="AV15" s="15" t="s">
+      <c r="AX15" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="AW15" s="14" t="s">
+      <c r="AY15" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3212,7 +3224,7 @@
       <c r="AI16" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="AW16" s="17" t="s">
+      <c r="AY16" s="17" t="s">
         <v>301</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F833C4-5544-4EDF-89CF-A523BF5242FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54125C3-2251-40FA-A4F0-496869890F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="418">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1285,6 +1285,15 @@
   </si>
   <si>
     <t>Обновление child_test</t>
+  </si>
+  <si>
+    <t>Стратегию по типу ST9 из VT</t>
+  </si>
+  <si>
+    <t>PWS2_DIRDC</t>
+  </si>
+  <si>
+    <t>PWS2_DIRATR</t>
   </si>
 </sst>
 </file>
@@ -1789,17 +1798,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="24" width="28.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="28.42578125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="27.42578125" style="2" customWidth="1"/>
-    <col min="27" max="110" width="27.28515625" style="2" customWidth="1"/>
-    <col min="111" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="24" width="28.26953125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.453125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="27.453125" style="2" customWidth="1"/>
+    <col min="27" max="110" width="27.26953125" style="2" customWidth="1"/>
+    <col min="111" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="3">
         <v>45747</v>
@@ -2129,7 +2138,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2248,7 +2257,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2355,7 +2364,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:110" ht="87" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:110" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:110" ht="116" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2539,7 +2548,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2625,7 +2634,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2708,7 +2717,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2757,6 +2766,9 @@
       <c r="AM8" s="4" t="s">
         <v>403</v>
       </c>
+      <c r="AQ8" s="2" t="s">
+        <v>415</v>
+      </c>
       <c r="AT8" s="2" t="s">
         <v>318</v>
       </c>
@@ -2782,7 +2794,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2848,7 +2860,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2916,7 +2928,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2962,6 +2974,9 @@
       <c r="AM11" s="4" t="s">
         <v>398</v>
       </c>
+      <c r="AN11" s="4" t="s">
+        <v>416</v>
+      </c>
       <c r="AW11" s="15" t="s">
         <v>252</v>
       </c>
@@ -2978,7 +2993,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:110" ht="87" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3024,6 +3039,9 @@
       <c r="AM12" s="4" t="s">
         <v>399</v>
       </c>
+      <c r="AN12" s="4" t="s">
+        <v>417</v>
+      </c>
       <c r="AW12" s="16" t="s">
         <v>292</v>
       </c>
@@ -3037,7 +3055,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="58" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3093,7 +3111,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3143,7 +3161,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3193,7 +3211,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:110" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3228,7 +3246,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3260,7 +3278,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3289,7 +3307,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3315,7 +3333,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3341,7 +3359,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3361,7 +3379,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3378,7 +3396,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3395,7 +3413,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3412,7 +3430,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3429,7 +3447,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3443,7 +3461,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3454,7 +3472,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3465,7 +3483,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3476,7 +3494,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3487,7 +3505,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3498,7 +3516,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3506,7 +3524,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -3514,92 +3532,92 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3613,19 +3631,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FB18B6-8CBA-4D69-B652-AA868883124A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="10"/>
-    <col min="2" max="2" width="54.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="10"/>
+    <col min="2" max="2" width="54.81640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="45.1796875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -3644,13 +3662,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BCABFF-B4AE-4771-9DE2-5CE17DADACE8}">
   <dimension ref="A2:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" style="18" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="36.7265625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3658,7 +3676,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3666,7 +3684,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3674,7 +3692,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3682,7 +3700,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3690,7 +3708,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3698,7 +3716,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3706,97 +3724,97 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\dev\RichLaughter2\_other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54125C3-2251-40FA-A4F0-496869890F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60888EEF-0D16-41AA-9119-0B46EF656A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="422">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1294,6 +1294,18 @@
   </si>
   <si>
     <t>PWS2_DIRATR</t>
+  </si>
+  <si>
+    <t>Добавить по времени закрытие, как в RL2 в VT5</t>
+  </si>
+  <si>
+    <t>ЗАКРЫТИЕ ПЕРЕД СПИСАНИЕМ ФАНДИНГА ДЛЯ ВЕЧНЫХ ФЬЮЧЕРСОВ</t>
+  </si>
+  <si>
+    <t>Добавить в тест подсчет дней и прибыль в день</t>
+  </si>
+  <si>
+    <t>Изучить тассадара</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1399,12 +1411,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1440,7 +1446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1499,10 +1505,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1512,9 +1518,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1798,17 +1801,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DF51"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="24" width="28.26953125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="28.453125" style="2" customWidth="1"/>
-    <col min="26" max="26" width="27.453125" style="2" customWidth="1"/>
-    <col min="27" max="110" width="27.26953125" style="2" customWidth="1"/>
-    <col min="111" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="24" width="28.28515625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="27.42578125" style="2" customWidth="1"/>
+    <col min="27" max="110" width="27.28515625" style="2" customWidth="1"/>
+    <col min="111" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3">
         <v>45747</v>
@@ -2138,7 +2141,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2223,10 +2226,13 @@
       <c r="AN2" s="4" t="s">
         <v>408</v>
       </c>
+      <c r="AP2" s="2" t="s">
+        <v>421</v>
+      </c>
       <c r="AQ2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AR2" s="22" t="s">
+      <c r="AR2" s="21" t="s">
         <v>384</v>
       </c>
       <c r="AS2" s="2" t="s">
@@ -2235,7 +2241,7 @@
       <c r="AT2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="AU2" s="22" t="s">
+      <c r="AU2" s="21" t="s">
         <v>314</v>
       </c>
       <c r="AV2" s="2" t="s">
@@ -2257,7 +2263,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:110" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2333,16 +2339,16 @@
       <c r="AQ3" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AR3" s="23" t="s">
+      <c r="AR3" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="AS3" s="22" t="s">
+      <c r="AS3" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="AT3" s="22" t="s">
+      <c r="AT3" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="AU3" s="22" t="s">
+      <c r="AU3" s="21" t="s">
         <v>315</v>
       </c>
       <c r="AV3" s="2" t="s">
@@ -2364,7 +2370,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:110" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2428,16 +2434,13 @@
       <c r="AN4" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="AQ4" s="20" t="s">
-        <v>396</v>
-      </c>
       <c r="AR4" s="2" t="s">
         <v>400</v>
       </c>
       <c r="AS4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AT4" s="21" t="s">
+      <c r="AT4" s="20" t="s">
         <v>370</v>
       </c>
       <c r="AU4" s="2" t="s">
@@ -2462,7 +2465,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:110" ht="116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:110" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2514,16 +2517,19 @@
       <c r="AM5" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="AQ5" s="23" t="s">
+      <c r="AN5" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="AQ5" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="AR5" s="23" t="s">
+      <c r="AR5" s="22" t="s">
         <v>402</v>
       </c>
       <c r="AS5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AT5" s="23" t="s">
+      <c r="AT5" s="22" t="s">
         <v>371</v>
       </c>
       <c r="AU5" s="2" t="s">
@@ -2548,7 +2554,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2606,13 +2612,16 @@
       <c r="AM6" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="AQ6" s="25" t="s">
+      <c r="AN6" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="AQ6" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="AT6" s="22" t="s">
+      <c r="AT6" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="AU6" s="21" t="s">
+      <c r="AU6" s="20" t="s">
         <v>349</v>
       </c>
       <c r="AV6" s="2" t="s">
@@ -2634,7 +2643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2689,13 +2698,16 @@
       <c r="AM7" s="4" t="s">
         <v>404</v>
       </c>
+      <c r="AN7" s="4" t="s">
+        <v>418</v>
+      </c>
       <c r="AQ7" s="2" t="s">
         <v>412</v>
       </c>
       <c r="AT7" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AU7" s="21" t="s">
+      <c r="AU7" s="20" t="s">
         <v>323</v>
       </c>
       <c r="AV7" s="2" t="s">
@@ -2717,7 +2729,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:110" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -2766,6 +2778,9 @@
       <c r="AM8" s="4" t="s">
         <v>403</v>
       </c>
+      <c r="AN8" s="4" t="s">
+        <v>396</v>
+      </c>
       <c r="AQ8" s="2" t="s">
         <v>415</v>
       </c>
@@ -2794,7 +2809,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2843,7 +2858,7 @@
       <c r="AT9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="AU9" s="21" t="s">
+      <c r="AU9" s="20" t="s">
         <v>405</v>
       </c>
       <c r="AV9" s="2" t="s">
@@ -2852,7 +2867,7 @@
       <c r="AW9" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="AX9" s="21"/>
+      <c r="AX9" s="20"/>
       <c r="AY9" s="14" t="s">
         <v>220</v>
       </c>
@@ -2860,7 +2875,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -2906,7 +2921,7 @@
       <c r="AT10" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="AU10" s="21" t="s">
+      <c r="AU10" s="20" t="s">
         <v>407</v>
       </c>
       <c r="AV10" s="2" t="s">
@@ -2928,7 +2943,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -2993,7 +3008,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:110" ht="87" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3055,7 +3070,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -3098,10 +3113,10 @@
       <c r="AJ13" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="AW13" s="24" t="s">
+      <c r="AW13" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="AX13" s="24" t="s">
+      <c r="AX13" s="23" t="s">
         <v>263</v>
       </c>
       <c r="AY13" s="16" t="s">
@@ -3111,7 +3126,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3154,14 +3169,14 @@
       <c r="AW14" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="AX14" s="24" t="s">
+      <c r="AX14" s="23" t="s">
         <v>267</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -3211,7 +3226,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:110" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3246,7 +3261,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3278,7 +3293,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3307,7 +3322,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3333,7 +3348,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3359,7 +3374,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3379,7 +3394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3396,7 +3411,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3413,7 +3428,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3430,7 +3445,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3447,7 +3462,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3461,7 +3476,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3472,7 +3487,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3483,7 +3498,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3494,7 +3509,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3505,7 +3520,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3516,7 +3531,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -3524,7 +3539,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -3532,92 +3547,92 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3631,19 +3646,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0FB18B6-8CBA-4D69-B652-AA868883124A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="10"/>
-    <col min="2" max="2" width="54.81640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="45.1796875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="10"/>
+    <col min="2" max="2" width="54.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -3662,13 +3677,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BCABFF-B4AE-4771-9DE2-5CE17DADACE8}">
   <dimension ref="A2:B27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" customWidth="1"/>
-    <col min="2" max="2" width="36.7265625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3676,7 +3691,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3684,7 +3699,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3692,7 +3707,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3700,7 +3715,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3708,7 +3723,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3716,7 +3731,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3724,97 +3739,97 @@
         <v>337</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60888EEF-0D16-41AA-9119-0B46EF656A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286CD67-3209-4F3D-A983-E4FD8E7B2EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="427">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1306,6 +1306,21 @@
   </si>
   <si>
     <t>Изучить тассадара</t>
+  </si>
+  <si>
+    <t>Попробовать написать арбитражные стратегии и протестировать. Если норм, то написать такую возможность для VT5 и полностью перевести один проп на арбитраж</t>
+  </si>
+  <si>
+    <t>Добавить открыватель позиций по условию. К примеру, цена ниже или выше уровня. RL2</t>
+  </si>
+  <si>
+    <t>SCAWS2_SHARKNADO</t>
+  </si>
+  <si>
+    <t>OpenWSCondition</t>
+  </si>
+  <si>
+    <t>Скрининг фандинга</t>
   </si>
 </sst>
 </file>
@@ -2227,7 +2242,7 @@
         <v>408</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AQ2" s="2" t="s">
         <v>394</v>
@@ -2434,6 +2449,9 @@
       <c r="AN4" s="4" t="s">
         <v>414</v>
       </c>
+      <c r="AQ4" s="2" t="s">
+        <v>422</v>
+      </c>
       <c r="AR4" s="2" t="s">
         <v>400</v>
       </c>
@@ -2855,6 +2873,9 @@
       <c r="AM9" s="4" t="s">
         <v>410</v>
       </c>
+      <c r="AN9" s="4" t="s">
+        <v>421</v>
+      </c>
       <c r="AT9" s="2" t="s">
         <v>344</v>
       </c>
@@ -2918,6 +2939,9 @@
       <c r="AM10" s="4" t="s">
         <v>397</v>
       </c>
+      <c r="AN10" s="4" t="s">
+        <v>423</v>
+      </c>
       <c r="AT10" s="2" t="s">
         <v>406</v>
       </c>
@@ -3113,6 +3137,9 @@
       <c r="AJ13" s="4" t="s">
         <v>381</v>
       </c>
+      <c r="AN13" s="4" t="s">
+        <v>424</v>
+      </c>
       <c r="AW13" s="23" t="s">
         <v>256</v>
       </c>
@@ -3165,6 +3192,9 @@
       </c>
       <c r="AI14" s="4" t="s">
         <v>361</v>
+      </c>
+      <c r="AN14" s="4" t="s">
+        <v>425</v>
       </c>
       <c r="AW14" s="15" t="s">
         <v>266</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A286CD67-3209-4F3D-A983-E4FD8E7B2EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC70609-E94B-4D97-8558-10AC70615B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="444">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1321,6 +1321,57 @@
   </si>
   <si>
     <t>Скрининг фандинга</t>
+  </si>
+  <si>
+    <t>Сброщик спреда для VT</t>
+  </si>
+  <si>
+    <t>Реверс-хедж автоматизировать</t>
+  </si>
+  <si>
+    <t>Хеджирующий по краям грид. В конце с небольшим буфером для избежания дребезжания. Сделки совершаются одновременно. Должен спасать от больших движений. Ну и можно без страха собирать волатильность. Ту мач надо сделать</t>
+  </si>
+  <si>
+    <t>Добавить пару на все торгуемые инструменты. Типа если был RM-3, то пара к нему RM-6. BR-1 и BR-2. В общем, это для тех у кого нет вечного фьюча</t>
+  </si>
+  <si>
+    <t>E-сетка (RL2)</t>
+  </si>
+  <si>
+    <t>Ползающая пара (RL2)</t>
+  </si>
+  <si>
+    <t>Арбитражный грид</t>
+  </si>
+  <si>
+    <t>RSI-хедж</t>
+  </si>
+  <si>
+    <t>СС-хедж</t>
+  </si>
+  <si>
+    <t>Грид с плавающим размером позиций</t>
+  </si>
+  <si>
+    <t>Самоопределяющая сетка по шагу</t>
+  </si>
+  <si>
+    <t>Сбрасыватель позиций по RSI</t>
+  </si>
+  <si>
+    <t>Определитель уровней по срез-максу с минимальным шагом</t>
+  </si>
+  <si>
+    <t>Грид по срез-максу</t>
+  </si>
+  <si>
+    <t>грид по дельте срез-макса</t>
+  </si>
+  <si>
+    <t>парный грид по срез-максу</t>
+  </si>
+  <si>
+    <t>LWS8_SINGULARITY</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1402,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1448,6 +1499,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1461,7 +1518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1533,6 +1590,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2241,44 +2301,47 @@
       <c r="AN2" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AO2" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AR2" s="21" t="s">
+      <c r="AT2" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="AU2" s="21" t="s">
+      <c r="AW2" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="AW2" s="13" t="s">
+      <c r="AY2" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="AX2" s="14" t="s">
+      <c r="AZ2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="AY2" s="13" t="s">
+      <c r="BA2" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AZ2" s="15" t="s">
+      <c r="BB2" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="BA2" s="13" t="s">
+      <c r="BC2" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2351,37 +2414,43 @@
       <c r="AN3" s="4" t="s">
         <v>413</v>
       </c>
+      <c r="AO3" s="25" t="s">
+        <v>429</v>
+      </c>
       <c r="AQ3" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AR3" s="22" t="s">
+      <c r="AT3" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="AS3" s="21" t="s">
+      <c r="AU3" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="AT3" s="21" t="s">
+      <c r="AV3" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="AU3" s="21" t="s">
+      <c r="AW3" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AX3" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AW3" s="14" t="s">
+      <c r="AY3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="AX3" s="16" t="s">
+      <c r="AZ3" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="AY3" s="13" t="s">
+      <c r="BA3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AZ3" s="16" t="s">
+      <c r="BB3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="BA3" s="14" t="s">
+      <c r="BC3" s="14" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2449,37 +2518,34 @@
       <c r="AN4" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="AQ4" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="AS4" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="AU4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AT4" s="20" t="s">
+      <c r="AV4" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="AU4" s="2" t="s">
+      <c r="AW4" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AV4" s="2" t="s">
+      <c r="AX4" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AW4" s="13" t="s">
+      <c r="AY4" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AX4" s="15" t="s">
+      <c r="AZ4" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AY4" s="13" t="s">
+      <c r="BA4" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AZ4" s="16" t="s">
+      <c r="BB4" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="BA4" s="16" t="s">
+      <c r="BC4" s="16" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2538,37 +2604,40 @@
       <c r="AN5" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="AQ5" s="22" t="s">
+      <c r="AR5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="AS5" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="AR5" s="22" t="s">
+      <c r="AT5" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="AS5" s="2" t="s">
+      <c r="AU5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AT5" s="22" t="s">
+      <c r="AV5" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="AU5" s="2" t="s">
+      <c r="AW5" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AV5" s="2" t="s">
+      <c r="AX5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AW5" s="14" t="s">
+      <c r="AY5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="AX5" s="15" t="s">
+      <c r="AZ5" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="AY5" s="13" t="s">
+      <c r="BA5" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AZ5" s="16" t="s">
+      <c r="BB5" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="BA5" s="14" t="s">
+      <c r="BC5" s="14" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2633,31 +2702,34 @@
       <c r="AN6" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="AQ6" s="24" t="s">
+      <c r="AR6" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="AS6" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="AT6" s="21" t="s">
+      <c r="AV6" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="AU6" s="20" t="s">
+      <c r="AW6" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="AV6" s="2" t="s">
+      <c r="AX6" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AW6" s="14" t="s">
+      <c r="AY6" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="AX6" s="15" t="s">
+      <c r="AZ6" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AY6" s="13" t="s">
+      <c r="BA6" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AZ6" s="15" t="s">
+      <c r="BB6" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="BA6" s="13" t="s">
+      <c r="BC6" s="13" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2719,31 +2791,31 @@
       <c r="AN7" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="AQ7" s="2" t="s">
+      <c r="AS7" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="AT7" s="2" t="s">
+      <c r="AV7" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AU7" s="20" t="s">
+      <c r="AW7" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="AV7" s="2" t="s">
+      <c r="AX7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AW7" s="14" t="s">
+      <c r="AY7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="AX7" s="15" t="s">
+      <c r="AZ7" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AY7" s="13" t="s">
+      <c r="BA7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AZ7" s="13" t="s">
+      <c r="BB7" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="BA7" s="13" t="s">
+      <c r="BC7" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2799,31 +2871,34 @@
       <c r="AN8" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="AQ8" s="2" t="s">
+      <c r="AR8" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="AS8" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="AT8" s="2" t="s">
+      <c r="AV8" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AU8" s="2" t="s">
+      <c r="AW8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AV8" s="2" t="s">
+      <c r="AX8" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AW8" s="14" t="s">
+      <c r="AY8" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="AX8" s="14" t="s">
+      <c r="AZ8" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="AY8" s="13" t="s">
+      <c r="BA8" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AZ8" s="14" t="s">
+      <c r="BB8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="BA8" s="15" t="s">
+      <c r="BC8" s="15" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2876,23 +2951,29 @@
       <c r="AN9" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="AT9" s="2" t="s">
+      <c r="AR9" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="AS9" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="AV9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="AU9" s="20" t="s">
+      <c r="AW9" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="AV9" s="2" t="s">
+      <c r="AX9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AW9" s="13" t="s">
+      <c r="AY9" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="AX9" s="20"/>
-      <c r="AY9" s="14" t="s">
+      <c r="AZ9" s="20"/>
+      <c r="BA9" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="BA9" s="14" t="s">
+      <c r="BC9" s="14" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2942,28 +3023,34 @@
       <c r="AN10" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="AT10" s="2" t="s">
+      <c r="AR10" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="AV10" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="AU10" s="20" t="s">
+      <c r="AW10" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="AV10" s="2" t="s">
+      <c r="AX10" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AW10" s="15" t="s">
+      <c r="AY10" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="AX10" s="15" t="s">
+      <c r="AZ10" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="AY10" s="14" t="s">
+      <c r="BA10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="AZ10" s="13" t="s">
+      <c r="BB10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BA10" s="13" t="s">
+      <c r="BC10" s="13" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3016,19 +3103,25 @@
       <c r="AN11" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="AW11" s="15" t="s">
+      <c r="AR11" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="AY11" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="AX11" s="15" t="s">
+      <c r="AZ11" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="AY11" s="14" t="s">
+      <c r="BA11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="AZ11" s="13" t="s">
+      <c r="BB11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="BA11" s="14" t="s">
+      <c r="BC11" s="14" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3081,16 +3174,22 @@
       <c r="AN12" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="AW12" s="16" t="s">
+      <c r="AR12" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="AS12" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="AY12" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="AX12" s="14" t="s">
+      <c r="AZ12" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AY12" s="15" t="s">
+      <c r="BA12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="AZ12" s="14" t="s">
+      <c r="BB12" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3140,16 +3239,19 @@
       <c r="AN13" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="AW13" s="23" t="s">
+      <c r="AR13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="AY13" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="AX13" s="23" t="s">
+      <c r="AZ13" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="AY13" s="16" t="s">
+      <c r="BA13" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="AZ13" s="13" t="s">
+      <c r="BB13" s="13" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3196,13 +3298,16 @@
       <c r="AN14" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="AW14" s="15" t="s">
+      <c r="AR14" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="AY14" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="AX14" s="23" t="s">
+      <c r="AZ14" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="AY14" s="14" t="s">
+      <c r="BA14" s="14" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3246,13 +3351,19 @@
       <c r="AI15" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="AW15" s="13" t="s">
+      <c r="AN15" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="AR15" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="AY15" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="AX15" s="15" t="s">
+      <c r="AZ15" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="AY15" s="14" t="s">
+      <c r="BA15" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3287,7 +3398,7 @@
       <c r="AI16" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="AY16" s="17" t="s">
+      <c r="BA16" s="17" t="s">
         <v>301</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC70609-E94B-4D97-8558-10AC70615B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE29CA35-2B70-4525-8994-5CF129E95C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="445">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1329,9 +1329,6 @@
     <t>Реверс-хедж автоматизировать</t>
   </si>
   <si>
-    <t>Хеджирующий по краям грид. В конце с небольшим буфером для избежания дребезжания. Сделки совершаются одновременно. Должен спасать от больших движений. Ну и можно без страха собирать волатильность. Ту мач надо сделать</t>
-  </si>
-  <si>
     <t>Добавить пару на все торгуемые инструменты. Типа если был RM-3, то пара к нему RM-6. BR-1 и BR-2. В общем, это для тех у кого нет вечного фьюча</t>
   </si>
   <si>
@@ -1372,6 +1369,12 @@
   </si>
   <si>
     <t>LWS8_SINGULARITY</t>
+  </si>
+  <si>
+    <t>Плавающий грид-диапазон по ADX</t>
+  </si>
+  <si>
+    <t>LWS8_GRAVITON</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2305,7 @@
         <v>408</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ2" s="2" t="s">
         <v>426</v>
@@ -2341,7 +2344,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="165" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2414,9 +2417,7 @@
       <c r="AN3" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="AO3" s="25" t="s">
-        <v>429</v>
-      </c>
+      <c r="AO3" s="25"/>
       <c r="AQ3" s="2" t="s">
         <v>422</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v>396</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AS8" s="2" t="s">
         <v>415</v>
@@ -2952,10 +2953,10 @@
         <v>421</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AS9" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AV9" s="2" t="s">
         <v>344</v>
@@ -3024,10 +3025,10 @@
         <v>423</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AS10" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AV10" s="2" t="s">
         <v>406</v>
@@ -3104,10 +3105,10 @@
         <v>416</v>
       </c>
       <c r="AR11" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AS11" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AY11" s="15" t="s">
         <v>252</v>
@@ -3175,10 +3176,10 @@
         <v>417</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AS12" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AY12" s="16" t="s">
         <v>292</v>
@@ -3240,7 +3241,10 @@
         <v>424</v>
       </c>
       <c r="AR13" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
+      </c>
+      <c r="AS13" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="AY13" s="23" t="s">
         <v>256</v>
@@ -3299,7 +3303,7 @@
         <v>425</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AY14" s="15" t="s">
         <v>266</v>
@@ -3352,10 +3356,10 @@
         <v>362</v>
       </c>
       <c r="AN15" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AR15" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AY15" s="13" t="s">
         <v>279</v>
@@ -3397,6 +3401,9 @@
       </c>
       <c r="AI16" s="4" t="s">
         <v>363</v>
+      </c>
+      <c r="AN16" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="BA16" s="17" t="s">
         <v>301</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE29CA35-2B70-4525-8994-5CF129E95C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66A20A5-1928-45A0-8F8D-479B1B2A2994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="447">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1329,9 +1329,6 @@
     <t>Реверс-хедж автоматизировать</t>
   </si>
   <si>
-    <t>Добавить пару на все торгуемые инструменты. Типа если был RM-3, то пара к нему RM-6. BR-1 и BR-2. В общем, это для тех у кого нет вечного фьюча</t>
-  </si>
-  <si>
     <t>E-сетка (RL2)</t>
   </si>
   <si>
@@ -1375,6 +1372,15 @@
   </si>
   <si>
     <t>LWS8_GRAVITON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавить пару на все торгуемые инструменты. </t>
+  </si>
+  <si>
+    <t>Арбитраж + сбор фандинга стратегия.</t>
+  </si>
+  <si>
+    <t>APSWS1_DYNAMO</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1502,12 +1508,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1521,7 +1521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1593,9 +1593,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2304,10 +2301,7 @@
       <c r="AN2" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="AO2" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>426</v>
       </c>
       <c r="AS2" s="2" t="s">
@@ -2417,8 +2411,8 @@
       <c r="AN3" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="AO3" s="25"/>
-      <c r="AQ3" s="2" t="s">
+      <c r="AO3" s="20"/>
+      <c r="AR3" s="2" t="s">
         <v>422</v>
       </c>
       <c r="AS3" s="2" t="s">
@@ -2519,6 +2513,9 @@
       <c r="AN4" s="4" t="s">
         <v>414</v>
       </c>
+      <c r="AR4" s="2" t="s">
+        <v>445</v>
+      </c>
       <c r="AS4" s="2" t="s">
         <v>427</v>
       </c>
@@ -2792,6 +2789,9 @@
       <c r="AN7" s="4" t="s">
         <v>418</v>
       </c>
+      <c r="AR7" s="2" t="s">
+        <v>436</v>
+      </c>
       <c r="AS7" s="2" t="s">
         <v>412</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>396</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AS8" s="2" t="s">
         <v>415</v>
@@ -2953,10 +2953,10 @@
         <v>421</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS9" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AV9" s="2" t="s">
         <v>344</v>
@@ -3025,10 +3025,10 @@
         <v>423</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AS10" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AV10" s="2" t="s">
         <v>406</v>
@@ -3102,13 +3102,13 @@
         <v>398</v>
       </c>
       <c r="AN11" s="4" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="AR11" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AS11" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AY11" s="15" t="s">
         <v>252</v>
@@ -3173,13 +3173,13 @@
         <v>399</v>
       </c>
       <c r="AN12" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AS12" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AY12" s="16" t="s">
         <v>292</v>
@@ -3238,13 +3238,13 @@
         <v>381</v>
       </c>
       <c r="AN13" s="4" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AR13" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AS13" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AY13" s="23" t="s">
         <v>256</v>
@@ -3300,10 +3300,10 @@
         <v>361</v>
       </c>
       <c r="AN14" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AY14" s="15" t="s">
         <v>266</v>
@@ -3356,10 +3356,7 @@
         <v>362</v>
       </c>
       <c r="AN15" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="AR15" s="2" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="AY15" s="13" t="s">
         <v>279</v>
@@ -3403,13 +3400,13 @@
         <v>363</v>
       </c>
       <c r="AN16" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="BA16" s="17" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -3440,8 +3437,11 @@
       <c r="AI17" s="4" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AN17" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -3469,8 +3469,11 @@
       <c r="AI18" s="4" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AN18" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -3496,7 +3499,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3522,7 +3525,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -3542,7 +3545,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -3559,7 +3562,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -3576,7 +3579,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -3610,7 +3613,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -3624,7 +3627,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -3635,7 +3638,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -3657,7 +3660,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -3679,7 +3682,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66A20A5-1928-45A0-8F8D-479B1B2A2994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD02B5F-68B2-4CDA-A6BF-CB4AD3F13A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="448">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1381,6 +1381,9 @@
   </si>
   <si>
     <t>APSWS1_DYNAMO</t>
+  </si>
+  <si>
+    <t>Добавить в сингулярность возможность держать стартовые позиции до финиша. Таким образом будет удобно переводить сделки в новый диапазон</t>
   </si>
 </sst>
 </file>
@@ -2301,8 +2304,8 @@
       <c r="AN2" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="AR2" s="2" t="s">
-        <v>426</v>
+      <c r="AO2" s="4" t="s">
+        <v>445</v>
       </c>
       <c r="AS2" s="2" t="s">
         <v>394</v>
@@ -2411,7 +2414,9 @@
       <c r="AN3" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="AO3" s="20"/>
+      <c r="AO3" s="4" t="s">
+        <v>447</v>
+      </c>
       <c r="AR3" s="2" t="s">
         <v>422</v>
       </c>
@@ -2513,8 +2518,8 @@
       <c r="AN4" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="AR4" s="2" t="s">
-        <v>445</v>
+      <c r="AO4" s="4" t="s">
+        <v>426</v>
       </c>
       <c r="AS4" s="2" t="s">
         <v>427</v>
@@ -3175,6 +3180,9 @@
       <c r="AN12" s="4" t="s">
         <v>416</v>
       </c>
+      <c r="AO12" s="4" t="s">
+        <v>446</v>
+      </c>
       <c r="AR12" s="2" t="s">
         <v>433</v>
       </c>
@@ -3468,9 +3476,6 @@
       </c>
       <c r="AI18" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="AN18" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD02B5F-68B2-4CDA-A6BF-CB4AD3F13A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A610408D-FBE1-4241-94CC-E7056097E265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="451">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1384,6 +1384,16 @@
   </si>
   <si>
     <t>Добавить в сингулярность возможность держать стартовые позиции до финиша. Таким образом будет удобно переводить сделки в новый диапазон</t>
+  </si>
+  <si>
+    <t>APSWS2_SPARTACUS</t>
+  </si>
+  <si>
+    <t>Посмотреть, почему сообщение о заявке отображается много раз.
+Исправил</t>
+  </si>
+  <si>
+    <t>Удерживающая стратегия до прибыли/безубытка по RSI и BB</t>
   </si>
 </sst>
 </file>
@@ -2307,6 +2317,9 @@
       <c r="AO2" s="4" t="s">
         <v>445</v>
       </c>
+      <c r="AR2" s="2" t="s">
+        <v>422</v>
+      </c>
       <c r="AS2" s="2" t="s">
         <v>394</v>
       </c>
@@ -2341,7 +2354,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:110" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2416,9 +2429,6 @@
       </c>
       <c r="AO3" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="AS3" s="2" t="s">
         <v>395</v>
@@ -2607,6 +2617,9 @@
       <c r="AN5" s="4" t="s">
         <v>420</v>
       </c>
+      <c r="AO5" s="4" t="s">
+        <v>449</v>
+      </c>
       <c r="AR5" s="2" t="s">
         <v>400</v>
       </c>
@@ -3248,6 +3261,9 @@
       <c r="AN13" s="4" t="s">
         <v>417</v>
       </c>
+      <c r="AO13" s="4" t="s">
+        <v>448</v>
+      </c>
       <c r="AR13" s="2" t="s">
         <v>434</v>
       </c>
@@ -3267,7 +3283,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3312,6 +3328,9 @@
       </c>
       <c r="AR14" s="2" t="s">
         <v>435</v>
+      </c>
+      <c r="AS14" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="AY14" s="15" t="s">
         <v>266</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A610408D-FBE1-4241-94CC-E7056097E265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E4B184-1686-4D9C-B53E-865F39766F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="454">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1394,6 +1394,15 @@
   </si>
   <si>
     <t>Удерживающая стратегия до прибыли/безубытка по RSI и BB</t>
+  </si>
+  <si>
+    <t>поиск диапазона по средним вершинам с хеджем в паре</t>
+  </si>
+  <si>
+    <t>APSWS3_PROMETHEUS</t>
+  </si>
+  <si>
+    <t>Вечная плавающая сетка с хеджированием вверху с фиксированным шагом. Надо подумать только над лимитными границами. А так она бы могла самостоятельно ползать</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1433,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1521,6 +1530,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1534,7 +1549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1606,6 +1621,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2430,6 +2448,9 @@
       <c r="AO3" s="4" t="s">
         <v>447</v>
       </c>
+      <c r="AR3" s="2" t="s">
+        <v>451</v>
+      </c>
       <c r="AS3" s="2" t="s">
         <v>395</v>
       </c>
@@ -2531,6 +2552,9 @@
       <c r="AO4" s="4" t="s">
         <v>426</v>
       </c>
+      <c r="AR4" s="25" t="s">
+        <v>453</v>
+      </c>
       <c r="AS4" s="2" t="s">
         <v>427</v>
       </c>
@@ -3325,6 +3349,9 @@
       </c>
       <c r="AN14" s="4" t="s">
         <v>424</v>
+      </c>
+      <c r="AO14" s="4" t="s">
+        <v>452</v>
       </c>
       <c r="AR14" s="2" t="s">
         <v>435</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E4B184-1686-4D9C-B53E-865F39766F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84DF979-39EC-4778-BEE3-9B27B66DBF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="455">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1403,6 +1403,9 @@
   </si>
   <si>
     <t>Вечная плавающая сетка с хеджированием вверху с фиксированным шагом. Надо подумать только над лимитными границами. А так она бы могла самостоятельно ползать</t>
+  </si>
+  <si>
+    <t>LWS8_LITE</t>
   </si>
 </sst>
 </file>
@@ -2742,6 +2745,9 @@
       <c r="AN6" s="4" t="s">
         <v>419</v>
       </c>
+      <c r="AO6" s="4" t="s">
+        <v>446</v>
+      </c>
       <c r="AR6" s="2" t="s">
         <v>428</v>
       </c>
@@ -2831,6 +2837,9 @@
       <c r="AN7" s="4" t="s">
         <v>418</v>
       </c>
+      <c r="AO7" s="4" t="s">
+        <v>448</v>
+      </c>
       <c r="AR7" s="2" t="s">
         <v>436</v>
       </c>
@@ -2914,6 +2923,9 @@
       <c r="AN8" s="4" t="s">
         <v>396</v>
       </c>
+      <c r="AO8" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="AR8" s="2" t="s">
         <v>430</v>
       </c>
@@ -2994,6 +3006,9 @@
       <c r="AN9" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="AP9" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="AR9" s="2" t="s">
         <v>429</v>
       </c>
@@ -3217,9 +3232,6 @@
       <c r="AN12" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="AO12" s="4" t="s">
-        <v>446</v>
-      </c>
       <c r="AR12" s="2" t="s">
         <v>433</v>
       </c>
@@ -3285,9 +3297,6 @@
       <c r="AN13" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="AO13" s="4" t="s">
-        <v>448</v>
-      </c>
       <c r="AR13" s="2" t="s">
         <v>434</v>
       </c>
@@ -3349,9 +3358,6 @@
       </c>
       <c r="AN14" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="AO14" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="AR14" s="2" t="s">
         <v>435</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84DF979-39EC-4778-BEE3-9B27B66DBF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5161B4-E834-41C5-8D0D-877CB9ACC247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="460">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1406,6 +1406,21 @@
   </si>
   <si>
     <t>LWS8_LITE</t>
+  </si>
+  <si>
+    <t>Сетка со старом уровней в лонг/шорт и другими уровнями для закрытия</t>
+  </si>
+  <si>
+    <t>LWS8_LITE с закрытием в середине</t>
+  </si>
+  <si>
+    <t>SCAWS1_mini</t>
+  </si>
+  <si>
+    <t>Сбрасыватель позиции по RSI</t>
+  </si>
+  <si>
+    <t>трейлинг-хедж</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1451,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1539,6 +1554,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1552,7 +1573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1627,6 +1648,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2338,6 +2362,12 @@
       <c r="AO2" s="4" t="s">
         <v>445</v>
       </c>
+      <c r="AP2" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>455</v>
+      </c>
       <c r="AR2" s="2" t="s">
         <v>422</v>
       </c>
@@ -2451,6 +2481,12 @@
       <c r="AO3" s="4" t="s">
         <v>447</v>
       </c>
+      <c r="AP3" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>456</v>
+      </c>
       <c r="AR3" s="2" t="s">
         <v>451</v>
       </c>
@@ -2554,6 +2590,9 @@
       </c>
       <c r="AO4" s="4" t="s">
         <v>426</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>459</v>
       </c>
       <c r="AR4" s="25" t="s">
         <v>453</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter2\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5161B4-E834-41C5-8D0D-877CB9ACC247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C0A592-38B6-400C-B17E-E117C9971F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Идеи" sheetId="2" r:id="rId2"/>
     <sheet name="ТезисыRL2" sheetId="3" r:id="rId3"/>
+    <sheet name="ДрБотов" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="506">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1421,6 +1422,144 @@
   </si>
   <si>
     <t>трейлинг-хедж</t>
+  </si>
+  <si>
+    <t>непропорциональный хедж</t>
+  </si>
+  <si>
+    <t>Evolutionist3</t>
+  </si>
+  <si>
+    <t>NLSTA1_UNION</t>
+  </si>
+  <si>
+    <t>Написать свой Cscalp (мини). Просто стакан, для быстрых заявок. Можно просто сделать 3 кнопки. Объем 1,0,-1. И просто выставлять по самой лучшей цене, как обычно.</t>
+  </si>
+  <si>
+    <t>Настроить подключение VT</t>
+  </si>
+  <si>
+    <t>Расширить VT на работу по стакану</t>
+  </si>
+  <si>
+    <t>Роботы сборщики спреда</t>
+  </si>
+  <si>
+    <t>Обучить NLSTA под дешевые  инструменты VT</t>
+  </si>
+  <si>
+    <t>Написать RL-обучение под нейронки</t>
+  </si>
+  <si>
+    <t>Разделитель на VT</t>
+  </si>
+  <si>
+    <t>не забыть убрать настройку затемнения</t>
+  </si>
+  <si>
+    <t>Робот прострельщик</t>
+  </si>
+  <si>
+    <t>Научить VT ставить уровни на графике</t>
+  </si>
+  <si>
+    <t>Научить VT выставлять каскад заявок на прострел</t>
+  </si>
+  <si>
+    <t>adx + кросс 2 sma можно определять текущее направление или боковик</t>
+  </si>
+  <si>
+    <t>автоматизировать сбор роботов через повторяющиеся паттерны в ленте</t>
+  </si>
+  <si>
+    <t>Автоматизировать сбор айсбергов через кластеры</t>
+  </si>
+  <si>
+    <t>Почистить RL</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>К</t>
+  </si>
+  <si>
+    <t>PTA</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Сборщик отскоков от плотностей в стакане с учетом тренда</t>
+  </si>
+  <si>
+    <t>PTA30_LILI</t>
+  </si>
+  <si>
+    <t>Надо реализовать алгоритм сбора спреда, а потом уже переходить к нейронкам и иным идеям</t>
+  </si>
+  <si>
+    <t>PTA30_RAYNOR</t>
+  </si>
+  <si>
+    <t>Сборщие отскоков с минимальным профитом и стоп-лоссом</t>
+  </si>
+  <si>
+    <t>VT6</t>
+  </si>
+  <si>
+    <t>ЦАТ</t>
+  </si>
+  <si>
+    <t>Новый VisualTrader с распознаванием полных баров.</t>
+  </si>
+  <si>
+    <t>Evol3 с отложенными свечами</t>
+  </si>
+  <si>
+    <t>Evol3 с точками зигаза / их отношением</t>
+  </si>
+  <si>
+    <t>Попробовать реализовать сбор заколотых имбалансов</t>
+  </si>
+  <si>
+    <t>Выбирать самый большой бар за N свечей и после него искать самый высокий/низкий фрактал, но не ниже самого имбаланса</t>
+  </si>
+  <si>
+    <t>Так же надо подумать над тем, как избежать заторгованного имбаланса и какой будет стоп/тейк</t>
+  </si>
+  <si>
+    <t>Вообще, надо попробовать прям реализовать концепцию смартмани, вса, побарки, прайсэкшен</t>
+  </si>
+  <si>
+    <t>Нужен тест с отложенными заявками</t>
+  </si>
+  <si>
+    <t>Надо убрать роботов из оптимизации, которые работают с будущим (ну и создать планы на переделывание их)</t>
+  </si>
+  <si>
+    <t>Сборщик спреда</t>
+  </si>
+  <si>
+    <t>Выставлять заявки large с минимальным шагом</t>
+  </si>
+  <si>
+    <t>Высталять заявки по шагу</t>
+  </si>
+  <si>
+    <t>Доработать выставление заявок по уровням</t>
+  </si>
+  <si>
+    <t>Есть какой-то баг, что первую сделку заключает сразу же при старте VT и по рынку</t>
+  </si>
+  <si>
+    <t>Пофиксил случайные  Z !</t>
+  </si>
+  <si>
+    <t>Решить проблему ошибочного измерения размера прибыли и убытка, так же разобраться с предельными значениями</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1653,6 +1792,10 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2362,47 +2505,74 @@
       <c r="AO2" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="AP2" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AP2" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="AW2" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AT2" s="21" t="s">
+      <c r="AZ2" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="AW2" s="21" t="s">
+      <c r="BC2" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="AY2" s="13" t="s">
+      <c r="BE2" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="AZ2" s="14" t="s">
+      <c r="BF2" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="BA2" s="13" t="s">
+      <c r="BG2" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="BB2" s="15" t="s">
+      <c r="BH2" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="BC2" s="13" t="s">
+      <c r="BI2" s="13" t="s">
         <v>96</v>
+      </c>
+      <c r="BO2" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="BP2" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="BQ2" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="BT2" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="BU2" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="BV2" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="BW2" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:110" ht="90" x14ac:dyDescent="0.25">
@@ -2481,47 +2651,65 @@
       <c r="AO3" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="AP3" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AP3" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="AW3" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AX3" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AY3" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AT3" s="22" t="s">
+      <c r="AZ3" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="AU3" s="21" t="s">
+      <c r="BA3" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="AV3" s="21" t="s">
+      <c r="BB3" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="AW3" s="21" t="s">
+      <c r="BC3" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="BD3" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AY3" s="14" t="s">
+      <c r="BE3" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="AZ3" s="16" t="s">
+      <c r="BF3" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="BA3" s="13" t="s">
+      <c r="BG3" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="BB3" s="16" t="s">
+      <c r="BH3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="BC3" s="14" t="s">
+      <c r="BI3" s="14" t="s">
         <v>62</v>
+      </c>
+      <c r="BO3" s="27" t="s">
+        <v>470</v>
+      </c>
+      <c r="BP3" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="BQ3" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
@@ -2591,41 +2779,65 @@
       <c r="AO4" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="AQ4" s="2" t="s">
+      <c r="AP4" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="AW4" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="AR4" s="25" t="s">
+      <c r="AX4" s="25" t="s">
         <v>453</v>
       </c>
-      <c r="AS4" s="2" t="s">
+      <c r="AY4" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="AU4" s="2" t="s">
+      <c r="BA4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AV4" s="20" t="s">
+      <c r="BB4" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="AW4" s="2" t="s">
+      <c r="BC4" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AX4" s="2" t="s">
+      <c r="BD4" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AY4" s="13" t="s">
+      <c r="BE4" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="AZ4" s="15" t="s">
+      <c r="BF4" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="BA4" s="13" t="s">
+      <c r="BG4" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="BB4" s="16" t="s">
+      <c r="BH4" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="BC4" s="16" t="s">
+      <c r="BI4" s="16" t="s">
         <v>117</v>
+      </c>
+      <c r="BO4" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="BP4" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="BQ4" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="BW4" s="2" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:110" ht="135" x14ac:dyDescent="0.25">
@@ -2686,41 +2898,65 @@
       <c r="AO5" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="AR5" s="2" t="s">
+      <c r="AP5" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="AX5" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="AS5" s="22" t="s">
+      <c r="AY5" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="AT5" s="22" t="s">
+      <c r="AZ5" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="AU5" s="2" t="s">
+      <c r="BA5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AV5" s="22" t="s">
+      <c r="BB5" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="AW5" s="2" t="s">
+      <c r="BC5" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AX5" s="2" t="s">
+      <c r="BD5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AY5" s="14" t="s">
+      <c r="BE5" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="AZ5" s="15" t="s">
+      <c r="BF5" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="BA5" s="13" t="s">
+      <c r="BG5" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="BB5" s="16" t="s">
+      <c r="BH5" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="BC5" s="14" t="s">
+      <c r="BI5" s="14" t="s">
         <v>119</v>
+      </c>
+      <c r="BO5" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="BP5" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="BV5" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2787,35 +3023,47 @@
       <c r="AO6" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="AR6" s="2" t="s">
+      <c r="AW6" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX6" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="AS6" s="24" t="s">
+      <c r="AY6" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="AV6" s="21" t="s">
+      <c r="BB6" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="AW6" s="20" t="s">
+      <c r="BC6" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="AX6" s="2" t="s">
+      <c r="BD6" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AY6" s="14" t="s">
+      <c r="BE6" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="AZ6" s="15" t="s">
+      <c r="BF6" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="BA6" s="13" t="s">
+      <c r="BG6" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BB6" s="15" t="s">
+      <c r="BH6" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="BC6" s="13" t="s">
+      <c r="BI6" s="13" t="s">
         <v>120</v>
+      </c>
+      <c r="BP6" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="BV6" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2879,35 +3127,38 @@
       <c r="AO7" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AX7" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="AS7" s="2" t="s">
+      <c r="AY7" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="AV7" s="2" t="s">
+      <c r="BB7" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AW7" s="20" t="s">
+      <c r="BC7" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="AX7" s="2" t="s">
+      <c r="BD7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AY7" s="14" t="s">
+      <c r="BE7" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="AZ7" s="15" t="s">
+      <c r="BF7" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="BA7" s="13" t="s">
+      <c r="BG7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BB7" s="13" t="s">
+      <c r="BH7" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="BC7" s="13" t="s">
+      <c r="BI7" s="13" t="s">
         <v>121</v>
+      </c>
+      <c r="BP7" s="4" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
@@ -2965,35 +3216,41 @@
       <c r="AO8" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AX8" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="AS8" s="2" t="s">
+      <c r="AY8" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="AV8" s="2" t="s">
+      <c r="BB8" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AW8" s="2" t="s">
+      <c r="BC8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AX8" s="2" t="s">
+      <c r="BD8" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AY8" s="14" t="s">
+      <c r="BE8" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="AZ8" s="14" t="s">
+      <c r="BF8" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="BA8" s="13" t="s">
+      <c r="BG8" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="BB8" s="14" t="s">
+      <c r="BH8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="BC8" s="15" t="s">
+      <c r="BI8" s="15" t="s">
         <v>161</v>
+      </c>
+      <c r="BP8" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="BQ8" s="4" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -3045,32 +3302,29 @@
       <c r="AN9" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="AP9" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="AR9" s="2" t="s">
+      <c r="AX9" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="AS9" s="22" t="s">
+      <c r="AY9" s="22" t="s">
         <v>437</v>
       </c>
-      <c r="AV9" s="2" t="s">
+      <c r="BB9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="AW9" s="20" t="s">
+      <c r="BC9" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="AX9" s="2" t="s">
+      <c r="BD9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AY9" s="13" t="s">
+      <c r="BE9" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="AZ9" s="20"/>
-      <c r="BA9" s="14" t="s">
+      <c r="BF9" s="20"/>
+      <c r="BG9" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="BC9" s="14" t="s">
+      <c r="BI9" s="14" t="s">
         <v>167</v>
       </c>
     </row>
@@ -3120,34 +3374,34 @@
       <c r="AN10" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="AR10" s="2" t="s">
+      <c r="AX10" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="AS10" s="2" t="s">
+      <c r="AY10" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="AV10" s="2" t="s">
+      <c r="BB10" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="AW10" s="20" t="s">
+      <c r="BC10" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="AX10" s="2" t="s">
+      <c r="BD10" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AY10" s="15" t="s">
+      <c r="BE10" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="AZ10" s="15" t="s">
+      <c r="BF10" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="BA10" s="14" t="s">
+      <c r="BG10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="BB10" s="13" t="s">
+      <c r="BH10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="BC10" s="13" t="s">
+      <c r="BI10" s="13" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3200,25 +3454,25 @@
       <c r="AN11" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="AR11" s="2" t="s">
+      <c r="AX11" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="AS11" s="2" t="s">
+      <c r="AY11" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="AY11" s="15" t="s">
+      <c r="BE11" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="AZ11" s="15" t="s">
+      <c r="BF11" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="BA11" s="14" t="s">
+      <c r="BG11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="BB11" s="13" t="s">
+      <c r="BH11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="BC11" s="14" t="s">
+      <c r="BI11" s="14" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3271,22 +3525,22 @@
       <c r="AN12" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="AR12" s="2" t="s">
+      <c r="AX12" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="AS12" s="2" t="s">
+      <c r="AY12" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="AY12" s="16" t="s">
+      <c r="BE12" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="AZ12" s="14" t="s">
+      <c r="BF12" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="BA12" s="15" t="s">
+      <c r="BG12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="BB12" s="14" t="s">
+      <c r="BH12" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3336,22 +3590,22 @@
       <c r="AN13" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="AR13" s="2" t="s">
+      <c r="AX13" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="AS13" s="2" t="s">
+      <c r="AY13" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="AY13" s="23" t="s">
+      <c r="BE13" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="AZ13" s="23" t="s">
+      <c r="BF13" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="BA13" s="16" t="s">
+      <c r="BG13" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="BB13" s="13" t="s">
+      <c r="BH13" s="13" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3398,19 +3652,19 @@
       <c r="AN14" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="AR14" s="2" t="s">
+      <c r="AX14" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="AS14" s="2" t="s">
+      <c r="AY14" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="AY14" s="15" t="s">
+      <c r="BE14" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="AZ14" s="23" t="s">
+      <c r="BF14" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="BA14" s="14" t="s">
+      <c r="BG14" s="14" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3457,13 +3711,13 @@
       <c r="AN15" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="AY15" s="13" t="s">
+      <c r="BE15" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="AZ15" s="15" t="s">
+      <c r="BF15" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="BA15" s="14" t="s">
+      <c r="BG15" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3501,7 +3755,7 @@
       <c r="AN16" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="BA16" s="17" t="s">
+      <c r="BG16" s="17" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4084,4 +4338,2055 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0668382-D37B-4005-A9F4-51853B9CF4DF}">
+  <dimension ref="A1:E398"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="107.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C2" s="28">
+        <v>46212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C3" s="28">
+        <v>46217</v>
+      </c>
+      <c r="D3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="28">
+        <v>46219</v>
+      </c>
+      <c r="D4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>